--- a/data/gravel/Aurum Manto 2025.xlsx
+++ b/data/gravel/Aurum Manto 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149D6941-FA28-A54A-A067-3AC8E3B17951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011EEFEE-B5E7-2249-A421-D4260D51638B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2780" yWindow="960" windowWidth="26020" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -263,9 +263,6 @@
     <t>rider_max_spec</t>
   </si>
   <si>
-    <t>euros</t>
-  </si>
-  <si>
     <t>integrated</t>
   </si>
   <si>
@@ -351,6 +348,12 @@
   </si>
   <si>
     <t>Manto</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>https://aurumbikes.com/wp-content/uploads/2024/12/ARTIK-FC-SRAM-RED-1X.png</t>
   </si>
 </sst>
 </file>
@@ -741,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -749,7 +752,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -773,7 +776,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -781,7 +789,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -789,7 +797,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C8" s="5">
         <v>48</v>
@@ -813,7 +821,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9" s="6">
         <v>515</v>
@@ -836,7 +844,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C10" s="6">
         <v>380</v>
@@ -859,7 +867,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" s="6">
         <v>74.5</v>
@@ -882,7 +890,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" s="6">
         <v>518</v>
@@ -905,7 +913,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C13" s="6">
         <v>71.2</v>
@@ -928,7 +936,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" s="6">
         <v>50</v>
@@ -948,10 +956,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C15" s="6">
         <v>66</v>
@@ -974,7 +982,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" s="6">
         <v>425</v>
@@ -997,7 +1005,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C17" s="6">
         <v>77</v>
@@ -1017,10 +1025,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C18">
         <v>587</v>
@@ -1043,7 +1051,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C19" s="6">
         <v>423</v>
@@ -1066,7 +1074,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C20">
         <v>998</v>
@@ -1090,7 +1098,7 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C21">
         <v>704</v>
@@ -1113,7 +1121,7 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C22">
         <v>88</v>
@@ -1136,7 +1144,7 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C23" s="8">
         <v>395</v>
@@ -1315,7 +1323,7 @@
         <v>180.5</v>
       </c>
       <c r="G32" s="3">
-        <f t="shared" ref="D31:G32" si="2">G34</f>
+        <f t="shared" ref="G32" si="2">G34</f>
         <v>188</v>
       </c>
       <c r="H32" s="3"/>
@@ -1363,19 +1371,19 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C35" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="E35" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="F35" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="G35" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -1415,7 +1423,7 @@
         <v>31</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -1539,7 +1547,7 @@
         <v>51</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -1628,7 +1636,7 @@
         <v>65</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Aurum Manto 2025.xlsx
+++ b/data/gravel/Aurum Manto 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011EEFEE-B5E7-2249-A421-D4260D51638B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6377C767-8506-D940-B76F-A7803DCAC150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2780" yWindow="960" windowWidth="26020" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,12 @@
   </si>
   <si>
     <t>https://aurumbikes.com/wp-content/uploads/2024/12/ARTIK-FC-SRAM-RED-1X.png</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Pinto, Madrid, Spain</t>
   </si>
 </sst>
 </file>
@@ -733,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1639,6 +1645,14 @@
         <v>105</v>
       </c>
     </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>107</v>
+      </c>
+      <c r="B75" t="s">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Aurum Manto 2025.xlsx
+++ b/data/gravel/Aurum Manto 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6377C767-8506-D940-B76F-A7803DCAC150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3271380B-FD3F-BD48-B200-DE197AC1DB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2780" yWindow="960" windowWidth="26020" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,24 @@
   </si>
   <si>
     <t>Pinto, Madrid, Spain</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -739,7 +757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1496,160 +1514,190 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53">
-        <v>27.2</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B59">
+        <v>27.2</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>52</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>46</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>53</v>
-      </c>
-      <c r="B62" s="1"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>55</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B68" s="1"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>60</v>
-      </c>
-      <c r="B69" s="1"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>61</v>
-      </c>
-      <c r="B70" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
+      </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>63</v>
-      </c>
-      <c r="B72">
-        <v>5199</v>
+        <v>57</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B73" s="1"/>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>65</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>105</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B74" s="1"/>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>60</v>
+      </c>
+      <c r="B75" s="1"/>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>61</v>
+      </c>
+      <c r="B76" s="1"/>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>63</v>
+      </c>
+      <c r="B78">
+        <v>5199</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" s="1"/>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>107</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>108</v>
       </c>
     </row>
